--- a/source/guides/cdc/opioid-cds/ValueSet-pain-management-procedure.xlsx
+++ b/source/guides/cdc/opioid-cds/ValueSet-pain-management-procedure.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -29,10 +29,16 @@
     <t>http://fhir.org/guides/cdc/opioid-cds/ValueSet/pain-management-procedure</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.114222.48.34</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2022.1.0</t>
+    <t>2022.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -126,6 +132,9 @@
   </si>
   <si>
     <t>http://snomed.info/sct|http://snomed.info/sct/731000124108/version/20230301</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
   </si>
   <si>
     <t>Level</t>
@@ -283,7 +292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -408,6 +417,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -426,32 +443,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -461,12 +478,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>1</v>
@@ -474,10 +491,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -492,46 +517,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>35</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
